--- a/public/plantilla.xlsx
+++ b/public/plantilla.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wamp64\www\cargaHoraria\admin\configuraciones\estadisticas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wamp64\www\cargaHorariav2\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01F5BE69-2AA6-4019-971E-8558ADD37F07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35383822-DE6D-499D-8C04-8E3C36B4D4EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HORARIO BLANCO" sheetId="1" r:id="rId1"/>
@@ -117,7 +117,7 @@
     <t>DOCENTE</t>
   </si>
   <si>
-    <t>HORARIO CUATRIMESTRAL MAYO - AGOSTO 2025</t>
+    <t>HORARIO CUATRIMESTRAL SEPTIEMBRE - DICIEMBRE 2025</t>
   </si>
 </sst>
 </file>
@@ -705,6 +705,54 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -741,42 +789,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -827,18 +839,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1211,22 +1211,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Z977"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.42578125" customWidth="1"/>
-    <col min="2" max="6" width="40.42578125" customWidth="1"/>
-    <col min="7" max="7" width="43.7109375" customWidth="1"/>
-    <col min="8" max="26" width="13.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.44140625" customWidth="1"/>
+    <col min="2" max="6" width="40.44140625" customWidth="1"/>
+    <col min="7" max="7" width="43.6640625" customWidth="1"/>
+    <col min="8" max="26" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="91.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="34"/>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
+    <row r="1" spans="1:26" ht="91.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -1247,16 +1247,16 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="30" t="s">
+    <row r="2" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="37"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="25"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
@@ -1277,14 +1277,14 @@
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
     </row>
-    <row r="3" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="30" t="s">
+    <row r="3" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="40"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="28"/>
       <c r="F3" s="6" t="s">
         <v>0</v>
       </c>
@@ -1309,12 +1309,12 @@
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
     </row>
-    <row r="4" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="32"/>
-      <c r="B4" s="33"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="43"/>
+    <row r="4" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="20"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="31"/>
       <c r="F4" s="6" t="s">
         <v>1</v>
       </c>
@@ -1339,7 +1339,7 @@
       <c r="Y4" s="2"/>
       <c r="Z4" s="2"/>
     </row>
-    <row r="5" spans="1:26" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:26" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
@@ -1381,7 +1381,7 @@
       <c r="Y5" s="2"/>
       <c r="Z5" s="2"/>
     </row>
-    <row r="6" spans="1:26" ht="109.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" ht="109.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="11" t="s">
         <v>9</v>
       </c>
@@ -1411,7 +1411,7 @@
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
     </row>
-    <row r="7" spans="1:26" ht="109.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:26" ht="109.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="11" t="s">
         <v>10</v>
       </c>
@@ -1441,7 +1441,7 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8" spans="1:26" ht="108.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" ht="108.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
         <v>11</v>
       </c>
@@ -1471,7 +1471,7 @@
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
     </row>
-    <row r="9" spans="1:26" ht="108.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:26" ht="108.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="11" t="s">
         <v>12</v>
       </c>
@@ -1501,7 +1501,7 @@
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
     </row>
-    <row r="10" spans="1:26" ht="109.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" ht="109.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="11" t="s">
         <v>13</v>
       </c>
@@ -1531,7 +1531,7 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" spans="1:26" ht="109.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:26" ht="109.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
         <v>14</v>
       </c>
@@ -1561,7 +1561,7 @@
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
     </row>
-    <row r="12" spans="1:26" ht="109.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" ht="109.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="11" t="s">
         <v>15</v>
       </c>
@@ -1591,7 +1591,7 @@
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
     </row>
-    <row r="13" spans="1:26" ht="108.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:26" ht="108.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -1621,7 +1621,7 @@
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
     </row>
-    <row r="14" spans="1:26" ht="109.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" ht="109.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="11" t="s">
         <v>17</v>
       </c>
@@ -1651,7 +1651,7 @@
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
     </row>
-    <row r="15" spans="1:26" ht="109.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:26" ht="109.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -1681,7 +1681,7 @@
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
-    <row r="16" spans="1:26" ht="109.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" ht="109.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="11" t="s">
         <v>19</v>
       </c>
@@ -1711,7 +1711,7 @@
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" spans="1:26" ht="109.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:26" ht="109.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="11" t="s">
         <v>20</v>
       </c>
@@ -1741,7 +1741,7 @@
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
     </row>
-    <row r="18" spans="1:26" ht="108.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:26" ht="108.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="11" t="s">
         <v>21</v>
       </c>
@@ -1771,14 +1771,14 @@
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
     </row>
-    <row r="19" spans="1:26" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="38"/>
-      <c r="B19" s="38"/>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="38"/>
+    <row r="19" spans="1:26" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="26"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
@@ -1799,14 +1799,14 @@
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
     </row>
-    <row r="20" spans="1:26" ht="121.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="20"/>
-      <c r="B20" s="21"/>
-      <c r="C20" s="57"/>
-      <c r="D20" s="58"/>
-      <c r="E20" s="58"/>
-      <c r="F20" s="52"/>
-      <c r="G20" s="53"/>
+    <row r="20" spans="1:26" ht="121.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="38"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="61"/>
+      <c r="D20" s="62"/>
+      <c r="E20" s="62"/>
+      <c r="F20" s="56"/>
+      <c r="G20" s="57"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -1827,20 +1827,20 @@
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
     </row>
-    <row r="21" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="61" t="s">
+    <row r="21" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="62"/>
-      <c r="C21" s="14" t="s">
+      <c r="B21" s="15"/>
+      <c r="C21" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="D21" s="15"/>
-      <c r="E21" s="60"/>
-      <c r="F21" s="14" t="s">
+      <c r="D21" s="33"/>
+      <c r="E21" s="64"/>
+      <c r="F21" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="G21" s="15"/>
+      <c r="G21" s="33"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
@@ -1861,14 +1861,14 @@
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
     </row>
-    <row r="22" spans="1:26" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="63"/>
-      <c r="B22" s="64"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="54"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="17"/>
+    <row r="22" spans="1:26" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="16"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="58"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="35"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -1889,16 +1889,16 @@
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
     </row>
-    <row r="23" spans="1:26" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="16" t="s">
+    <row r="23" spans="1:26" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="54"/>
+      <c r="B23" s="35"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="58"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
@@ -1919,14 +1919,14 @@
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
     </row>
-    <row r="24" spans="1:26" ht="103.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="22"/>
-      <c r="B24" s="23"/>
-      <c r="C24" s="52"/>
-      <c r="D24" s="59"/>
-      <c r="E24" s="59"/>
-      <c r="F24" s="55"/>
-      <c r="G24" s="56"/>
+    <row r="24" spans="1:26" ht="103.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="40"/>
+      <c r="B24" s="41"/>
+      <c r="C24" s="56"/>
+      <c r="D24" s="63"/>
+      <c r="E24" s="63"/>
+      <c r="F24" s="59"/>
+      <c r="G24" s="60"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
@@ -1947,18 +1947,18 @@
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
     </row>
-    <row r="25" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="24"/>
-      <c r="B25" s="25"/>
-      <c r="C25" s="14" t="s">
+    <row r="25" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="42"/>
+      <c r="B25" s="43"/>
+      <c r="C25" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="46" t="s">
+      <c r="D25" s="33"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="G25" s="47"/>
+      <c r="G25" s="51"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
@@ -1979,14 +1979,14 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
-    <row r="26" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="26"/>
-      <c r="B26" s="27"/>
-      <c r="C26" s="44"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="48"/>
-      <c r="G26" s="49"/>
+    <row r="26" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="44"/>
+      <c r="B26" s="45"/>
+      <c r="C26" s="48"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="52"/>
+      <c r="G26" s="53"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
@@ -2007,16 +2007,16 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
     </row>
-    <row r="27" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="28" t="s">
+    <row r="27" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="29"/>
-      <c r="C27" s="44"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="45"/>
-      <c r="F27" s="48"/>
-      <c r="G27" s="49"/>
+      <c r="B27" s="47"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="49"/>
+      <c r="E27" s="49"/>
+      <c r="F27" s="52"/>
+      <c r="G27" s="53"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
@@ -2037,14 +2037,14 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="26"/>
-      <c r="B28" s="27"/>
-      <c r="C28" s="44"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="45"/>
-      <c r="F28" s="48"/>
-      <c r="G28" s="49"/>
+    <row r="28" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="44"/>
+      <c r="B28" s="45"/>
+      <c r="C28" s="48"/>
+      <c r="D28" s="49"/>
+      <c r="E28" s="49"/>
+      <c r="F28" s="52"/>
+      <c r="G28" s="53"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
@@ -2065,14 +2065,14 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
     </row>
-    <row r="29" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="18"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="50"/>
-      <c r="G29" s="51"/>
+    <row r="29" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="36"/>
+      <c r="B29" s="37"/>
+      <c r="C29" s="34"/>
+      <c r="D29" s="35"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="54"/>
+      <c r="G29" s="55"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
@@ -2093,7 +2093,7 @@
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
     </row>
-    <row r="30" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -2121,7 +2121,7 @@
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
     </row>
-    <row r="31" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -2149,7 +2149,7 @@
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
     </row>
-    <row r="32" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -2177,7 +2177,7 @@
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
     </row>
-    <row r="33" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -2205,7 +2205,7 @@
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
     </row>
-    <row r="34" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -2233,7 +2233,7 @@
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
     </row>
-    <row r="35" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -2261,7 +2261,7 @@
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
     </row>
-    <row r="36" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -2289,7 +2289,7 @@
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
     </row>
-    <row r="37" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -2317,7 +2317,7 @@
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
     </row>
-    <row r="38" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -2345,7 +2345,7 @@
       <c r="Y38" s="1"/>
       <c r="Z38" s="1"/>
     </row>
-    <row r="39" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -2373,7 +2373,7 @@
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
     </row>
-    <row r="40" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -2401,7 +2401,7 @@
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
     </row>
-    <row r="41" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -2429,7 +2429,7 @@
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
     </row>
-    <row r="42" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -2457,7 +2457,7 @@
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
     </row>
-    <row r="43" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -2485,7 +2485,7 @@
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
     </row>
-    <row r="44" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -2513,7 +2513,7 @@
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
     </row>
-    <row r="45" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -2541,7 +2541,7 @@
       <c r="Y45" s="1"/>
       <c r="Z45" s="1"/>
     </row>
-    <row r="46" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -2569,7 +2569,7 @@
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
     </row>
-    <row r="47" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -2597,7 +2597,7 @@
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
     </row>
-    <row r="48" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -2625,7 +2625,7 @@
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
     </row>
-    <row r="49" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -2653,7 +2653,7 @@
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
     </row>
-    <row r="50" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -2681,7 +2681,7 @@
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
     </row>
-    <row r="51" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -2709,7 +2709,7 @@
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
     </row>
-    <row r="52" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -2737,7 +2737,7 @@
       <c r="Y52" s="1"/>
       <c r="Z52" s="1"/>
     </row>
-    <row r="53" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -2765,7 +2765,7 @@
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
     </row>
-    <row r="54" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -2793,7 +2793,7 @@
       <c r="Y54" s="1"/>
       <c r="Z54" s="1"/>
     </row>
-    <row r="55" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -2821,7 +2821,7 @@
       <c r="Y55" s="1"/>
       <c r="Z55" s="1"/>
     </row>
-    <row r="56" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -2849,7 +2849,7 @@
       <c r="Y56" s="1"/>
       <c r="Z56" s="1"/>
     </row>
-    <row r="57" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -2877,7 +2877,7 @@
       <c r="Y57" s="1"/>
       <c r="Z57" s="1"/>
     </row>
-    <row r="58" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -2905,7 +2905,7 @@
       <c r="Y58" s="1"/>
       <c r="Z58" s="1"/>
     </row>
-    <row r="59" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -2933,7 +2933,7 @@
       <c r="Y59" s="1"/>
       <c r="Z59" s="1"/>
     </row>
-    <row r="60" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -2961,7 +2961,7 @@
       <c r="Y60" s="1"/>
       <c r="Z60" s="1"/>
     </row>
-    <row r="61" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -2989,7 +2989,7 @@
       <c r="Y61" s="1"/>
       <c r="Z61" s="1"/>
     </row>
-    <row r="62" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -3017,7 +3017,7 @@
       <c r="Y62" s="1"/>
       <c r="Z62" s="1"/>
     </row>
-    <row r="63" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -3045,7 +3045,7 @@
       <c r="Y63" s="1"/>
       <c r="Z63" s="1"/>
     </row>
-    <row r="64" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -3073,7 +3073,7 @@
       <c r="Y64" s="1"/>
       <c r="Z64" s="1"/>
     </row>
-    <row r="65" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -3101,7 +3101,7 @@
       <c r="Y65" s="1"/>
       <c r="Z65" s="1"/>
     </row>
-    <row r="66" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -3129,7 +3129,7 @@
       <c r="Y66" s="1"/>
       <c r="Z66" s="1"/>
     </row>
-    <row r="67" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -3157,7 +3157,7 @@
       <c r="Y67" s="1"/>
       <c r="Z67" s="1"/>
     </row>
-    <row r="68" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -3185,7 +3185,7 @@
       <c r="Y68" s="1"/>
       <c r="Z68" s="1"/>
     </row>
-    <row r="69" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -3213,7 +3213,7 @@
       <c r="Y69" s="1"/>
       <c r="Z69" s="1"/>
     </row>
-    <row r="70" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -3241,7 +3241,7 @@
       <c r="Y70" s="1"/>
       <c r="Z70" s="1"/>
     </row>
-    <row r="71" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -3269,7 +3269,7 @@
       <c r="Y71" s="1"/>
       <c r="Z71" s="1"/>
     </row>
-    <row r="72" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -3297,7 +3297,7 @@
       <c r="Y72" s="1"/>
       <c r="Z72" s="1"/>
     </row>
-    <row r="73" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -3325,7 +3325,7 @@
       <c r="Y73" s="1"/>
       <c r="Z73" s="1"/>
     </row>
-    <row r="74" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -3353,7 +3353,7 @@
       <c r="Y74" s="1"/>
       <c r="Z74" s="1"/>
     </row>
-    <row r="75" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -3381,7 +3381,7 @@
       <c r="Y75" s="1"/>
       <c r="Z75" s="1"/>
     </row>
-    <row r="76" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -3409,7 +3409,7 @@
       <c r="Y76" s="1"/>
       <c r="Z76" s="1"/>
     </row>
-    <row r="77" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -3437,7 +3437,7 @@
       <c r="Y77" s="1"/>
       <c r="Z77" s="1"/>
     </row>
-    <row r="78" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -3465,7 +3465,7 @@
       <c r="Y78" s="1"/>
       <c r="Z78" s="1"/>
     </row>
-    <row r="79" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -3493,7 +3493,7 @@
       <c r="Y79" s="1"/>
       <c r="Z79" s="1"/>
     </row>
-    <row r="80" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -3521,7 +3521,7 @@
       <c r="Y80" s="1"/>
       <c r="Z80" s="1"/>
     </row>
-    <row r="81" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -3549,7 +3549,7 @@
       <c r="Y81" s="1"/>
       <c r="Z81" s="1"/>
     </row>
-    <row r="82" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -3577,7 +3577,7 @@
       <c r="Y82" s="1"/>
       <c r="Z82" s="1"/>
     </row>
-    <row r="83" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -3605,7 +3605,7 @@
       <c r="Y83" s="1"/>
       <c r="Z83" s="1"/>
     </row>
-    <row r="84" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -3633,7 +3633,7 @@
       <c r="Y84" s="1"/>
       <c r="Z84" s="1"/>
     </row>
-    <row r="85" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -3661,7 +3661,7 @@
       <c r="Y85" s="1"/>
       <c r="Z85" s="1"/>
     </row>
-    <row r="86" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -3689,7 +3689,7 @@
       <c r="Y86" s="1"/>
       <c r="Z86" s="1"/>
     </row>
-    <row r="87" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -3717,7 +3717,7 @@
       <c r="Y87" s="1"/>
       <c r="Z87" s="1"/>
     </row>
-    <row r="88" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -3745,7 +3745,7 @@
       <c r="Y88" s="1"/>
       <c r="Z88" s="1"/>
     </row>
-    <row r="89" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -3773,7 +3773,7 @@
       <c r="Y89" s="1"/>
       <c r="Z89" s="1"/>
     </row>
-    <row r="90" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -3801,7 +3801,7 @@
       <c r="Y90" s="1"/>
       <c r="Z90" s="1"/>
     </row>
-    <row r="91" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -3829,7 +3829,7 @@
       <c r="Y91" s="1"/>
       <c r="Z91" s="1"/>
     </row>
-    <row r="92" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -3857,7 +3857,7 @@
       <c r="Y92" s="1"/>
       <c r="Z92" s="1"/>
     </row>
-    <row r="93" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -3885,7 +3885,7 @@
       <c r="Y93" s="1"/>
       <c r="Z93" s="1"/>
     </row>
-    <row r="94" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -3913,7 +3913,7 @@
       <c r="Y94" s="1"/>
       <c r="Z94" s="1"/>
     </row>
-    <row r="95" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -3941,7 +3941,7 @@
       <c r="Y95" s="1"/>
       <c r="Z95" s="1"/>
     </row>
-    <row r="96" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -3969,7 +3969,7 @@
       <c r="Y96" s="1"/>
       <c r="Z96" s="1"/>
     </row>
-    <row r="97" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -3997,7 +3997,7 @@
       <c r="Y97" s="1"/>
       <c r="Z97" s="1"/>
     </row>
-    <row r="98" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -4025,7 +4025,7 @@
       <c r="Y98" s="1"/>
       <c r="Z98" s="1"/>
     </row>
-    <row r="99" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -4053,7 +4053,7 @@
       <c r="Y99" s="1"/>
       <c r="Z99" s="1"/>
     </row>
-    <row r="100" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -4081,7 +4081,7 @@
       <c r="Y100" s="1"/>
       <c r="Z100" s="1"/>
     </row>
-    <row r="101" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -4109,7 +4109,7 @@
       <c r="Y101" s="1"/>
       <c r="Z101" s="1"/>
     </row>
-    <row r="102" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -4137,7 +4137,7 @@
       <c r="Y102" s="1"/>
       <c r="Z102" s="1"/>
     </row>
-    <row r="103" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -4165,7 +4165,7 @@
       <c r="Y103" s="1"/>
       <c r="Z103" s="1"/>
     </row>
-    <row r="104" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -4193,7 +4193,7 @@
       <c r="Y104" s="1"/>
       <c r="Z104" s="1"/>
     </row>
-    <row r="105" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -4221,7 +4221,7 @@
       <c r="Y105" s="1"/>
       <c r="Z105" s="1"/>
     </row>
-    <row r="106" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -4249,7 +4249,7 @@
       <c r="Y106" s="1"/>
       <c r="Z106" s="1"/>
     </row>
-    <row r="107" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -4277,7 +4277,7 @@
       <c r="Y107" s="1"/>
       <c r="Z107" s="1"/>
     </row>
-    <row r="108" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -4305,7 +4305,7 @@
       <c r="Y108" s="1"/>
       <c r="Z108" s="1"/>
     </row>
-    <row r="109" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -4333,7 +4333,7 @@
       <c r="Y109" s="1"/>
       <c r="Z109" s="1"/>
     </row>
-    <row r="110" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -4361,7 +4361,7 @@
       <c r="Y110" s="1"/>
       <c r="Z110" s="1"/>
     </row>
-    <row r="111" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -4389,7 +4389,7 @@
       <c r="Y111" s="1"/>
       <c r="Z111" s="1"/>
     </row>
-    <row r="112" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -4417,7 +4417,7 @@
       <c r="Y112" s="1"/>
       <c r="Z112" s="1"/>
     </row>
-    <row r="113" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -4445,7 +4445,7 @@
       <c r="Y113" s="1"/>
       <c r="Z113" s="1"/>
     </row>
-    <row r="114" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -4473,7 +4473,7 @@
       <c r="Y114" s="1"/>
       <c r="Z114" s="1"/>
     </row>
-    <row r="115" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -4501,7 +4501,7 @@
       <c r="Y115" s="1"/>
       <c r="Z115" s="1"/>
     </row>
-    <row r="116" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -4529,7 +4529,7 @@
       <c r="Y116" s="1"/>
       <c r="Z116" s="1"/>
     </row>
-    <row r="117" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -4557,7 +4557,7 @@
       <c r="Y117" s="1"/>
       <c r="Z117" s="1"/>
     </row>
-    <row r="118" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -4585,7 +4585,7 @@
       <c r="Y118" s="1"/>
       <c r="Z118" s="1"/>
     </row>
-    <row r="119" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -4613,7 +4613,7 @@
       <c r="Y119" s="1"/>
       <c r="Z119" s="1"/>
     </row>
-    <row r="120" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -4641,7 +4641,7 @@
       <c r="Y120" s="1"/>
       <c r="Z120" s="1"/>
     </row>
-    <row r="121" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -4669,7 +4669,7 @@
       <c r="Y121" s="1"/>
       <c r="Z121" s="1"/>
     </row>
-    <row r="122" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -4697,7 +4697,7 @@
       <c r="Y122" s="1"/>
       <c r="Z122" s="1"/>
     </row>
-    <row r="123" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -4725,7 +4725,7 @@
       <c r="Y123" s="1"/>
       <c r="Z123" s="1"/>
     </row>
-    <row r="124" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -4753,7 +4753,7 @@
       <c r="Y124" s="1"/>
       <c r="Z124" s="1"/>
     </row>
-    <row r="125" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -4781,7 +4781,7 @@
       <c r="Y125" s="1"/>
       <c r="Z125" s="1"/>
     </row>
-    <row r="126" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -4809,7 +4809,7 @@
       <c r="Y126" s="1"/>
       <c r="Z126" s="1"/>
     </row>
-    <row r="127" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -4837,7 +4837,7 @@
       <c r="Y127" s="1"/>
       <c r="Z127" s="1"/>
     </row>
-    <row r="128" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -4865,7 +4865,7 @@
       <c r="Y128" s="1"/>
       <c r="Z128" s="1"/>
     </row>
-    <row r="129" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -4893,7 +4893,7 @@
       <c r="Y129" s="1"/>
       <c r="Z129" s="1"/>
     </row>
-    <row r="130" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -4921,7 +4921,7 @@
       <c r="Y130" s="1"/>
       <c r="Z130" s="1"/>
     </row>
-    <row r="131" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -4949,7 +4949,7 @@
       <c r="Y131" s="1"/>
       <c r="Z131" s="1"/>
     </row>
-    <row r="132" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -4977,7 +4977,7 @@
       <c r="Y132" s="1"/>
       <c r="Z132" s="1"/>
     </row>
-    <row r="133" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -5005,7 +5005,7 @@
       <c r="Y133" s="1"/>
       <c r="Z133" s="1"/>
     </row>
-    <row r="134" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -5033,7 +5033,7 @@
       <c r="Y134" s="1"/>
       <c r="Z134" s="1"/>
     </row>
-    <row r="135" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -5061,7 +5061,7 @@
       <c r="Y135" s="1"/>
       <c r="Z135" s="1"/>
     </row>
-    <row r="136" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -5089,7 +5089,7 @@
       <c r="Y136" s="1"/>
       <c r="Z136" s="1"/>
     </row>
-    <row r="137" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -5117,7 +5117,7 @@
       <c r="Y137" s="1"/>
       <c r="Z137" s="1"/>
     </row>
-    <row r="138" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -5145,7 +5145,7 @@
       <c r="Y138" s="1"/>
       <c r="Z138" s="1"/>
     </row>
-    <row r="139" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -5173,7 +5173,7 @@
       <c r="Y139" s="1"/>
       <c r="Z139" s="1"/>
     </row>
-    <row r="140" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -5201,7 +5201,7 @@
       <c r="Y140" s="1"/>
       <c r="Z140" s="1"/>
     </row>
-    <row r="141" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -5229,7 +5229,7 @@
       <c r="Y141" s="1"/>
       <c r="Z141" s="1"/>
     </row>
-    <row r="142" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -5257,7 +5257,7 @@
       <c r="Y142" s="1"/>
       <c r="Z142" s="1"/>
     </row>
-    <row r="143" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -5285,7 +5285,7 @@
       <c r="Y143" s="1"/>
       <c r="Z143" s="1"/>
     </row>
-    <row r="144" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -5313,7 +5313,7 @@
       <c r="Y144" s="1"/>
       <c r="Z144" s="1"/>
     </row>
-    <row r="145" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -5341,7 +5341,7 @@
       <c r="Y145" s="1"/>
       <c r="Z145" s="1"/>
     </row>
-    <row r="146" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -5369,7 +5369,7 @@
       <c r="Y146" s="1"/>
       <c r="Z146" s="1"/>
     </row>
-    <row r="147" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -5397,7 +5397,7 @@
       <c r="Y147" s="1"/>
       <c r="Z147" s="1"/>
     </row>
-    <row r="148" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -5425,7 +5425,7 @@
       <c r="Y148" s="1"/>
       <c r="Z148" s="1"/>
     </row>
-    <row r="149" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -5453,7 +5453,7 @@
       <c r="Y149" s="1"/>
       <c r="Z149" s="1"/>
     </row>
-    <row r="150" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -5481,7 +5481,7 @@
       <c r="Y150" s="1"/>
       <c r="Z150" s="1"/>
     </row>
-    <row r="151" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -5509,7 +5509,7 @@
       <c r="Y151" s="1"/>
       <c r="Z151" s="1"/>
     </row>
-    <row r="152" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -5537,7 +5537,7 @@
       <c r="Y152" s="1"/>
       <c r="Z152" s="1"/>
     </row>
-    <row r="153" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -5565,7 +5565,7 @@
       <c r="Y153" s="1"/>
       <c r="Z153" s="1"/>
     </row>
-    <row r="154" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -5593,7 +5593,7 @@
       <c r="Y154" s="1"/>
       <c r="Z154" s="1"/>
     </row>
-    <row r="155" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -5621,7 +5621,7 @@
       <c r="Y155" s="1"/>
       <c r="Z155" s="1"/>
     </row>
-    <row r="156" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -5649,7 +5649,7 @@
       <c r="Y156" s="1"/>
       <c r="Z156" s="1"/>
     </row>
-    <row r="157" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -5677,7 +5677,7 @@
       <c r="Y157" s="1"/>
       <c r="Z157" s="1"/>
     </row>
-    <row r="158" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -5705,7 +5705,7 @@
       <c r="Y158" s="1"/>
       <c r="Z158" s="1"/>
     </row>
-    <row r="159" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -5733,7 +5733,7 @@
       <c r="Y159" s="1"/>
       <c r="Z159" s="1"/>
     </row>
-    <row r="160" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -5761,7 +5761,7 @@
       <c r="Y160" s="1"/>
       <c r="Z160" s="1"/>
     </row>
-    <row r="161" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -5789,7 +5789,7 @@
       <c r="Y161" s="1"/>
       <c r="Z161" s="1"/>
     </row>
-    <row r="162" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -5817,7 +5817,7 @@
       <c r="Y162" s="1"/>
       <c r="Z162" s="1"/>
     </row>
-    <row r="163" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -5845,7 +5845,7 @@
       <c r="Y163" s="1"/>
       <c r="Z163" s="1"/>
     </row>
-    <row r="164" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -5873,7 +5873,7 @@
       <c r="Y164" s="1"/>
       <c r="Z164" s="1"/>
     </row>
-    <row r="165" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -5901,7 +5901,7 @@
       <c r="Y165" s="1"/>
       <c r="Z165" s="1"/>
     </row>
-    <row r="166" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -5929,7 +5929,7 @@
       <c r="Y166" s="1"/>
       <c r="Z166" s="1"/>
     </row>
-    <row r="167" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -5957,7 +5957,7 @@
       <c r="Y167" s="1"/>
       <c r="Z167" s="1"/>
     </row>
-    <row r="168" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -5985,7 +5985,7 @@
       <c r="Y168" s="1"/>
       <c r="Z168" s="1"/>
     </row>
-    <row r="169" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -6013,7 +6013,7 @@
       <c r="Y169" s="1"/>
       <c r="Z169" s="1"/>
     </row>
-    <row r="170" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -6041,7 +6041,7 @@
       <c r="Y170" s="1"/>
       <c r="Z170" s="1"/>
     </row>
-    <row r="171" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -6069,7 +6069,7 @@
       <c r="Y171" s="1"/>
       <c r="Z171" s="1"/>
     </row>
-    <row r="172" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -6097,7 +6097,7 @@
       <c r="Y172" s="1"/>
       <c r="Z172" s="1"/>
     </row>
-    <row r="173" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -6125,7 +6125,7 @@
       <c r="Y173" s="1"/>
       <c r="Z173" s="1"/>
     </row>
-    <row r="174" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -6153,7 +6153,7 @@
       <c r="Y174" s="1"/>
       <c r="Z174" s="1"/>
     </row>
-    <row r="175" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -6181,7 +6181,7 @@
       <c r="Y175" s="1"/>
       <c r="Z175" s="1"/>
     </row>
-    <row r="176" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -6209,7 +6209,7 @@
       <c r="Y176" s="1"/>
       <c r="Z176" s="1"/>
     </row>
-    <row r="177" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -6237,7 +6237,7 @@
       <c r="Y177" s="1"/>
       <c r="Z177" s="1"/>
     </row>
-    <row r="178" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -6265,7 +6265,7 @@
       <c r="Y178" s="1"/>
       <c r="Z178" s="1"/>
     </row>
-    <row r="179" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -6293,7 +6293,7 @@
       <c r="Y179" s="1"/>
       <c r="Z179" s="1"/>
     </row>
-    <row r="180" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -6321,7 +6321,7 @@
       <c r="Y180" s="1"/>
       <c r="Z180" s="1"/>
     </row>
-    <row r="181" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -6349,7 +6349,7 @@
       <c r="Y181" s="1"/>
       <c r="Z181" s="1"/>
     </row>
-    <row r="182" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -6377,7 +6377,7 @@
       <c r="Y182" s="1"/>
       <c r="Z182" s="1"/>
     </row>
-    <row r="183" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -6405,7 +6405,7 @@
       <c r="Y183" s="1"/>
       <c r="Z183" s="1"/>
     </row>
-    <row r="184" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -6433,7 +6433,7 @@
       <c r="Y184" s="1"/>
       <c r="Z184" s="1"/>
     </row>
-    <row r="185" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -6461,7 +6461,7 @@
       <c r="Y185" s="1"/>
       <c r="Z185" s="1"/>
     </row>
-    <row r="186" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -6489,7 +6489,7 @@
       <c r="Y186" s="1"/>
       <c r="Z186" s="1"/>
     </row>
-    <row r="187" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -6517,7 +6517,7 @@
       <c r="Y187" s="1"/>
       <c r="Z187" s="1"/>
     </row>
-    <row r="188" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -6545,7 +6545,7 @@
       <c r="Y188" s="1"/>
       <c r="Z188" s="1"/>
     </row>
-    <row r="189" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -6573,7 +6573,7 @@
       <c r="Y189" s="1"/>
       <c r="Z189" s="1"/>
     </row>
-    <row r="190" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -6601,7 +6601,7 @@
       <c r="Y190" s="1"/>
       <c r="Z190" s="1"/>
     </row>
-    <row r="191" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -6629,7 +6629,7 @@
       <c r="Y191" s="1"/>
       <c r="Z191" s="1"/>
     </row>
-    <row r="192" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -6657,7 +6657,7 @@
       <c r="Y192" s="1"/>
       <c r="Z192" s="1"/>
     </row>
-    <row r="193" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -6685,7 +6685,7 @@
       <c r="Y193" s="1"/>
       <c r="Z193" s="1"/>
     </row>
-    <row r="194" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -6713,7 +6713,7 @@
       <c r="Y194" s="1"/>
       <c r="Z194" s="1"/>
     </row>
-    <row r="195" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -6741,7 +6741,7 @@
       <c r="Y195" s="1"/>
       <c r="Z195" s="1"/>
     </row>
-    <row r="196" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -6769,7 +6769,7 @@
       <c r="Y196" s="1"/>
       <c r="Z196" s="1"/>
     </row>
-    <row r="197" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -6797,7 +6797,7 @@
       <c r="Y197" s="1"/>
       <c r="Z197" s="1"/>
     </row>
-    <row r="198" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -6825,7 +6825,7 @@
       <c r="Y198" s="1"/>
       <c r="Z198" s="1"/>
     </row>
-    <row r="199" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -6853,7 +6853,7 @@
       <c r="Y199" s="1"/>
       <c r="Z199" s="1"/>
     </row>
-    <row r="200" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -6881,7 +6881,7 @@
       <c r="Y200" s="1"/>
       <c r="Z200" s="1"/>
     </row>
-    <row r="201" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -6909,7 +6909,7 @@
       <c r="Y201" s="1"/>
       <c r="Z201" s="1"/>
     </row>
-    <row r="202" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -6937,7 +6937,7 @@
       <c r="Y202" s="1"/>
       <c r="Z202" s="1"/>
     </row>
-    <row r="203" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -6965,7 +6965,7 @@
       <c r="Y203" s="1"/>
       <c r="Z203" s="1"/>
     </row>
-    <row r="204" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -6993,7 +6993,7 @@
       <c r="Y204" s="1"/>
       <c r="Z204" s="1"/>
     </row>
-    <row r="205" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -7021,7 +7021,7 @@
       <c r="Y205" s="1"/>
       <c r="Z205" s="1"/>
     </row>
-    <row r="206" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -7049,7 +7049,7 @@
       <c r="Y206" s="1"/>
       <c r="Z206" s="1"/>
     </row>
-    <row r="207" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -7077,7 +7077,7 @@
       <c r="Y207" s="1"/>
       <c r="Z207" s="1"/>
     </row>
-    <row r="208" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -7105,7 +7105,7 @@
       <c r="Y208" s="1"/>
       <c r="Z208" s="1"/>
     </row>
-    <row r="209" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -7133,7 +7133,7 @@
       <c r="Y209" s="1"/>
       <c r="Z209" s="1"/>
     </row>
-    <row r="210" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -7161,7 +7161,7 @@
       <c r="Y210" s="1"/>
       <c r="Z210" s="1"/>
     </row>
-    <row r="211" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -7189,7 +7189,7 @@
       <c r="Y211" s="1"/>
       <c r="Z211" s="1"/>
     </row>
-    <row r="212" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -7217,7 +7217,7 @@
       <c r="Y212" s="1"/>
       <c r="Z212" s="1"/>
     </row>
-    <row r="213" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -7245,7 +7245,7 @@
       <c r="Y213" s="1"/>
       <c r="Z213" s="1"/>
     </row>
-    <row r="214" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -7273,7 +7273,7 @@
       <c r="Y214" s="1"/>
       <c r="Z214" s="1"/>
     </row>
-    <row r="215" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -7301,7 +7301,7 @@
       <c r="Y215" s="1"/>
       <c r="Z215" s="1"/>
     </row>
-    <row r="216" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -7329,7 +7329,7 @@
       <c r="Y216" s="1"/>
       <c r="Z216" s="1"/>
     </row>
-    <row r="217" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -7357,7 +7357,7 @@
       <c r="Y217" s="1"/>
       <c r="Z217" s="1"/>
     </row>
-    <row r="218" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -7385,7 +7385,7 @@
       <c r="Y218" s="1"/>
       <c r="Z218" s="1"/>
     </row>
-    <row r="219" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -7413,7 +7413,7 @@
       <c r="Y219" s="1"/>
       <c r="Z219" s="1"/>
     </row>
-    <row r="220" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -7441,7 +7441,7 @@
       <c r="Y220" s="1"/>
       <c r="Z220" s="1"/>
     </row>
-    <row r="221" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -7469,7 +7469,7 @@
       <c r="Y221" s="1"/>
       <c r="Z221" s="1"/>
     </row>
-    <row r="222" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -7497,7 +7497,7 @@
       <c r="Y222" s="1"/>
       <c r="Z222" s="1"/>
     </row>
-    <row r="223" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -7525,7 +7525,7 @@
       <c r="Y223" s="1"/>
       <c r="Z223" s="1"/>
     </row>
-    <row r="224" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -7553,7 +7553,7 @@
       <c r="Y224" s="1"/>
       <c r="Z224" s="1"/>
     </row>
-    <row r="225" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -7581,7 +7581,7 @@
       <c r="Y225" s="1"/>
       <c r="Z225" s="1"/>
     </row>
-    <row r="226" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -7609,7 +7609,7 @@
       <c r="Y226" s="1"/>
       <c r="Z226" s="1"/>
     </row>
-    <row r="227" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -7637,7 +7637,7 @@
       <c r="Y227" s="1"/>
       <c r="Z227" s="1"/>
     </row>
-    <row r="228" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -7665,7 +7665,7 @@
       <c r="Y228" s="1"/>
       <c r="Z228" s="1"/>
     </row>
-    <row r="229" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -7693,769 +7693,756 @@
       <c r="Y229" s="1"/>
       <c r="Z229" s="1"/>
     </row>
-    <row r="230" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="231" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="232" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="233" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="234" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="235" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="236" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="237" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="238" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="239" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="240" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="231" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="232" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="233" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="234" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="235" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="236" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="237" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="238" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="239" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="240" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A21:B22"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="C3:E4"/>
-    <mergeCell ref="F21:G22"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A27:B27"/>
     <mergeCell ref="C25:E29"/>
     <mergeCell ref="F25:G29"/>
     <mergeCell ref="A28:B28"/>
@@ -8465,6 +8452,19 @@
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="C24:E24"/>
     <mergeCell ref="C21:E22"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A21:B22"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="C3:E4"/>
+    <mergeCell ref="F21:G22"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.22326454033771001" right="0.22326454033771001" top="0.20731707317073" bottom="0.22326454033771001" header="0" footer="0"/>

--- a/public/plantilla.xlsx
+++ b/public/plantilla.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wamp64\www\cargaHorariav2\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35383822-DE6D-499D-8C04-8E3C36B4D4EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2334DF6-CD04-4E54-A7AF-3CFD27FB3141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>Horas totales:</t>
   </si>
@@ -93,38 +93,32 @@
     <t>19:00 - 20:00</t>
   </si>
   <si>
-    <t>SUBDIRECTORA DE CARRERA</t>
-  </si>
-  <si>
     <t>DIRECTOR ACADÉMICO</t>
-  </si>
-  <si>
-    <t>SELLO PLANEACIÓN Y EVALUACIÓN</t>
-  </si>
-  <si>
-    <t>FIRMA DE CONOCIMIENTO</t>
   </si>
   <si>
     <t xml:space="preserve">SELLO DELEGACIÓN ADMINISTRATIVA                                         </t>
   </si>
   <si>
-    <t>COMISIÓN ACADÉMICA DICTAMINADORA</t>
-  </si>
-  <si>
     <t>Nombre del Docente:</t>
   </si>
   <si>
-    <t>DOCENTE</t>
+    <t>HORARIO CUATRIMESTRAL SEPTIEMBRE - DICIEMBRE 2025</t>
   </si>
   <si>
-    <t>HORARIO CUATRIMESTRAL SEPTIEMBRE - DICIEMBRE 2025</t>
+    <t>SUBDIRECCIÓN DE CARRERA</t>
+  </si>
+  <si>
+    <t>FIRMA DEL DOCENTE</t>
+  </si>
+  <si>
+    <t>COOMISIÓN INTERNA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -192,13 +186,6 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -237,7 +224,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="38">
+  <borders count="40">
     <border>
       <left/>
       <right/>
@@ -523,54 +510,12 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -662,11 +607,79 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -687,24 +700,84 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -753,91 +826,32 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1210,7 +1224,7 @@
     <tabColor rgb="FF4A86E8"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z977"/>
+  <dimension ref="A1:Z976"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.44140625" customWidth="1"/>
@@ -1220,13 +1234,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="91.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22"/>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
+      <c r="A1" s="46"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -1248,15 +1262,15 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
-        <v>30</v>
+      <c r="A2" s="42" t="s">
+        <v>25</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="25"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="49"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
@@ -1278,13 +1292,13 @@
       <c r="Z2" s="2"/>
     </row>
     <row r="3" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="18" t="s">
-        <v>28</v>
+      <c r="A3" s="42" t="s">
+        <v>24</v>
       </c>
-      <c r="B3" s="19"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="28"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="52"/>
       <c r="F3" s="6" t="s">
         <v>0</v>
       </c>
@@ -1310,11 +1324,11 @@
       <c r="Z3" s="2"/>
     </row>
     <row r="4" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="20"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="31"/>
+      <c r="A4" s="44"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="55"/>
       <c r="F4" s="6" t="s">
         <v>1</v>
       </c>
@@ -1772,13 +1786,13 @@
       <c r="Z18" s="1"/>
     </row>
     <row r="19" spans="1:26" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="26"/>
-      <c r="B19" s="26"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
+      <c r="A19" s="50"/>
+      <c r="B19" s="50"/>
+      <c r="C19" s="50"/>
+      <c r="D19" s="50"/>
+      <c r="E19" s="50"/>
+      <c r="F19" s="50"/>
+      <c r="G19" s="50"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
@@ -1800,13 +1814,13 @@
       <c r="Z19" s="1"/>
     </row>
     <row r="20" spans="1:26" ht="121.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="38"/>
-      <c r="B20" s="39"/>
-      <c r="C20" s="61"/>
-      <c r="D20" s="62"/>
-      <c r="E20" s="62"/>
-      <c r="F20" s="56"/>
-      <c r="G20" s="57"/>
+      <c r="A20" s="30"/>
+      <c r="B20" s="31"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="22"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -1828,19 +1842,19 @@
       <c r="Z20" s="1"/>
     </row>
     <row r="21" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="39"/>
+      <c r="C21" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="15"/>
-      <c r="C21" s="32" t="s">
-        <v>23</v>
+      <c r="D21" s="15"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="14" t="s">
+        <v>27</v>
       </c>
-      <c r="D21" s="33"/>
-      <c r="E21" s="64"/>
-      <c r="F21" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="G21" s="33"/>
+      <c r="G21" s="64"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
@@ -1862,13 +1876,13 @@
       <c r="Z21" s="1"/>
     </row>
     <row r="22" spans="1:26" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="16"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="34"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="58"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="35"/>
+      <c r="A22" s="40"/>
+      <c r="B22" s="41"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="65"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -1889,16 +1903,14 @@
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
     </row>
-    <row r="23" spans="1:26" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="35"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="35"/>
-      <c r="E23" s="35"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="58"/>
+    <row r="23" spans="1:26" ht="103.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="32"/>
+      <c r="B23" s="33"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="62"/>
+      <c r="G23" s="63"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
@@ -1919,14 +1931,16 @@
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
     </row>
-    <row r="24" spans="1:26" ht="103.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="40"/>
-      <c r="B24" s="41"/>
-      <c r="C24" s="56"/>
-      <c r="D24" s="63"/>
-      <c r="E24" s="63"/>
-      <c r="F24" s="59"/>
-      <c r="G24" s="60"/>
+    <row r="24" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="34"/>
+      <c r="B24" s="35"/>
+      <c r="C24" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" s="56"/>
+      <c r="E24" s="56"/>
+      <c r="F24" s="56"/>
+      <c r="G24" s="57"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
@@ -1948,17 +1962,13 @@
       <c r="Z24" s="1"/>
     </row>
     <row r="25" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="42"/>
-      <c r="B25" s="43"/>
-      <c r="C25" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="D25" s="33"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="50" t="s">
-        <v>29</v>
-      </c>
-      <c r="G25" s="51"/>
+      <c r="A25" s="19"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="56"/>
+      <c r="E25" s="56"/>
+      <c r="F25" s="56"/>
+      <c r="G25" s="57"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
@@ -1979,14 +1989,16 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
-    <row r="26" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="44"/>
-      <c r="B26" s="45"/>
-      <c r="C26" s="48"/>
-      <c r="D26" s="49"/>
-      <c r="E26" s="49"/>
-      <c r="F26" s="52"/>
-      <c r="G26" s="53"/>
+    <row r="26" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" s="37"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="56"/>
+      <c r="E26" s="56"/>
+      <c r="F26" s="56"/>
+      <c r="G26" s="57"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
@@ -2007,16 +2019,14 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
     </row>
-    <row r="27" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="46" t="s">
-        <v>26</v>
-      </c>
-      <c r="B27" s="47"/>
-      <c r="C27" s="48"/>
-      <c r="D27" s="49"/>
-      <c r="E27" s="49"/>
-      <c r="F27" s="52"/>
-      <c r="G27" s="53"/>
+    <row r="27" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="19"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="56"/>
+      <c r="E27" s="56"/>
+      <c r="F27" s="56"/>
+      <c r="G27" s="57"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
@@ -2037,14 +2047,14 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="44"/>
-      <c r="B28" s="45"/>
-      <c r="C28" s="48"/>
-      <c r="D28" s="49"/>
-      <c r="E28" s="49"/>
-      <c r="F28" s="52"/>
-      <c r="G28" s="53"/>
+    <row r="28" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="28"/>
+      <c r="B28" s="29"/>
+      <c r="C28" s="59"/>
+      <c r="D28" s="60"/>
+      <c r="E28" s="60"/>
+      <c r="F28" s="60"/>
+      <c r="G28" s="61"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
@@ -2065,14 +2075,14 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
     </row>
-    <row r="29" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="36"/>
-      <c r="B29" s="37"/>
-      <c r="C29" s="34"/>
-      <c r="D29" s="35"/>
-      <c r="E29" s="35"/>
-      <c r="F29" s="54"/>
-      <c r="G29" s="55"/>
+    <row r="29" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="58"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
@@ -7665,34 +7675,7 @@
       <c r="Y228" s="1"/>
       <c r="Z228" s="1"/>
     </row>
-    <row r="229" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A229" s="1"/>
-      <c r="B229" s="1"/>
-      <c r="C229" s="1"/>
-      <c r="D229" s="1"/>
-      <c r="E229" s="1"/>
-      <c r="F229" s="1"/>
-      <c r="G229" s="1"/>
-      <c r="H229" s="1"/>
-      <c r="I229" s="1"/>
-      <c r="J229" s="1"/>
-      <c r="K229" s="1"/>
-      <c r="L229" s="1"/>
-      <c r="M229" s="1"/>
-      <c r="N229" s="1"/>
-      <c r="O229" s="1"/>
-      <c r="P229" s="1"/>
-      <c r="Q229" s="1"/>
-      <c r="R229" s="1"/>
-      <c r="S229" s="1"/>
-      <c r="T229" s="1"/>
-      <c r="U229" s="1"/>
-      <c r="V229" s="1"/>
-      <c r="W229" s="1"/>
-      <c r="X229" s="1"/>
-      <c r="Y229" s="1"/>
-      <c r="Z229" s="1"/>
-    </row>
+    <row r="229" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="230" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="231" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="232" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -8440,31 +8423,28 @@
     <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="C25:E29"/>
-    <mergeCell ref="F25:G29"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C21:E22"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A21:B22"/>
+  <mergeCells count="20">
+    <mergeCell ref="F21:G22"/>
+    <mergeCell ref="C24:G28"/>
     <mergeCell ref="A3:B4"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A19:G19"/>
     <mergeCell ref="C3:E4"/>
-    <mergeCell ref="F21:G22"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C21:E22"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A21:B22"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.22326454033771001" right="0.22326454033771001" top="0.20731707317073" bottom="0.22326454033771001" header="0" footer="0"/>

--- a/public/plantilla.xlsx
+++ b/public/plantilla.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wamp64\www\cargaHorariav2\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2334DF6-CD04-4E54-A7AF-3CFD27FB3141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{501212BF-E2B4-4E43-B57B-D0AEDD042837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -426,17 +426,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
@@ -628,32 +617,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="medium">
         <color indexed="64"/>
@@ -675,11 +638,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -700,37 +700,88 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -743,19 +794,22 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -790,69 +844,14 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -914,18 +913,18 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>257175</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>247650</xdr:rowOff>
+      <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1828800" cy="847725"/>
+    <xdr:ext cx="1809750" cy="704850"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="image4.jpg">
+        <xdr:cNvPr id="4" name="image2.png">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -951,45 +950,65 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>352425</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>696686</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:rowOff>87086</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1809750" cy="704850"/>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2842986</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>1128486</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="image2.png">
+        <xdr:cNvPr id="5" name="Imagen 4" descr="Gobierno de Michoacán">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{718B394E-4A84-4A64-BE29-D7A6372D2BBB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect t="23392" b="28655"/>
+        <a:stretch/>
       </xdr:blipFill>
-      <xdr:spPr>
+      <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="16187057" y="87086"/>
+          <a:ext cx="2146300" cy="1041400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1234,13 +1253,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="91.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="46"/>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
+      <c r="A1" s="28"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -1262,15 +1281,15 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="49"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="31"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
@@ -1292,13 +1311,13 @@
       <c r="Z2" s="2"/>
     </row>
     <row r="3" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="43"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="52"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="34"/>
       <c r="F3" s="6" t="s">
         <v>0</v>
       </c>
@@ -1324,11 +1343,11 @@
       <c r="Z3" s="2"/>
     </row>
     <row r="4" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="44"/>
-      <c r="B4" s="45"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="55"/>
+      <c r="A4" s="26"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="37"/>
       <c r="F4" s="6" t="s">
         <v>1</v>
       </c>
@@ -1395,7 +1414,7 @@
       <c r="Y5" s="2"/>
       <c r="Z5" s="2"/>
     </row>
-    <row r="6" spans="1:26" ht="109.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:26" ht="22.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="11" t="s">
         <v>9</v>
       </c>
@@ -1425,7 +1444,7 @@
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
     </row>
-    <row r="7" spans="1:26" ht="109.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:26" ht="22.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="11" t="s">
         <v>10</v>
       </c>
@@ -1455,7 +1474,7 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8" spans="1:26" ht="108.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:26" ht="22.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
         <v>11</v>
       </c>
@@ -1485,7 +1504,7 @@
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
     </row>
-    <row r="9" spans="1:26" ht="108.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:26" ht="22.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="11" t="s">
         <v>12</v>
       </c>
@@ -1515,7 +1534,7 @@
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
     </row>
-    <row r="10" spans="1:26" ht="109.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:26" ht="22.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="11" t="s">
         <v>13</v>
       </c>
@@ -1545,7 +1564,7 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" spans="1:26" ht="109.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:26" ht="22.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
         <v>14</v>
       </c>
@@ -1575,7 +1594,7 @@
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
     </row>
-    <row r="12" spans="1:26" ht="109.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:26" ht="22.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="11" t="s">
         <v>15</v>
       </c>
@@ -1605,7 +1624,7 @@
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
     </row>
-    <row r="13" spans="1:26" ht="108.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:26" ht="22.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -1635,7 +1654,7 @@
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
     </row>
-    <row r="14" spans="1:26" ht="109.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:26" ht="22.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="11" t="s">
         <v>17</v>
       </c>
@@ -1665,7 +1684,7 @@
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
     </row>
-    <row r="15" spans="1:26" ht="109.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:26" ht="22.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -1695,7 +1714,7 @@
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
-    <row r="16" spans="1:26" ht="109.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:26" ht="22.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="11" t="s">
         <v>19</v>
       </c>
@@ -1725,7 +1744,7 @@
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" spans="1:26" ht="109.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:26" ht="22.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="11" t="s">
         <v>20</v>
       </c>
@@ -1755,7 +1774,7 @@
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
     </row>
-    <row r="18" spans="1:26" ht="108.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:26" ht="22.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="11" t="s">
         <v>21</v>
       </c>
@@ -1786,13 +1805,13 @@
       <c r="Z18" s="1"/>
     </row>
     <row r="19" spans="1:26" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="50"/>
-      <c r="B19" s="50"/>
-      <c r="C19" s="50"/>
-      <c r="D19" s="50"/>
-      <c r="E19" s="50"/>
-      <c r="F19" s="50"/>
-      <c r="G19" s="50"/>
+      <c r="A19" s="32"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
@@ -1814,13 +1833,13 @@
       <c r="Z19" s="1"/>
     </row>
     <row r="20" spans="1:26" ht="121.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="30"/>
-      <c r="B20" s="31"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="22"/>
+      <c r="A20" s="50"/>
+      <c r="B20" s="51"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="43"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="41"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -1842,19 +1861,19 @@
       <c r="Z20" s="1"/>
     </row>
     <row r="21" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="38" t="s">
+      <c r="A21" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="39"/>
+      <c r="B21" s="59"/>
       <c r="C21" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="D21" s="15"/>
-      <c r="E21" s="27"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="45"/>
       <c r="F21" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="G21" s="64"/>
+      <c r="G21" s="15"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
@@ -1876,13 +1895,13 @@
       <c r="Z21" s="1"/>
     </row>
     <row r="22" spans="1:26" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="40"/>
-      <c r="B22" s="41"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="65"/>
+      <c r="A22" s="60"/>
+      <c r="B22" s="61"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="46"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="17"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -1904,13 +1923,13 @@
       <c r="Z22" s="1"/>
     </row>
     <row r="23" spans="1:26" ht="103.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="32"/>
-      <c r="B23" s="33"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="63"/>
+      <c r="A23" s="52"/>
+      <c r="B23" s="53"/>
+      <c r="C23" s="62"/>
+      <c r="D23" s="63"/>
+      <c r="E23" s="63"/>
+      <c r="F23" s="63"/>
+      <c r="G23" s="64"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
@@ -1932,15 +1951,15 @@
       <c r="Z23" s="1"/>
     </row>
     <row r="24" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="34"/>
-      <c r="B24" s="35"/>
-      <c r="C24" s="16" t="s">
+      <c r="A24" s="54"/>
+      <c r="B24" s="55"/>
+      <c r="C24" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="D24" s="56"/>
-      <c r="E24" s="56"/>
-      <c r="F24" s="56"/>
-      <c r="G24" s="57"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="20"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
@@ -1962,13 +1981,13 @@
       <c r="Z24" s="1"/>
     </row>
     <row r="25" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="19"/>
-      <c r="B25" s="20"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="56"/>
-      <c r="E25" s="56"/>
-      <c r="F25" s="56"/>
-      <c r="G25" s="57"/>
+      <c r="A25" s="38"/>
+      <c r="B25" s="39"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="20"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
@@ -1990,15 +2009,15 @@
       <c r="Z25" s="1"/>
     </row>
     <row r="26" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="36" t="s">
+      <c r="A26" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="B26" s="37"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="56"/>
-      <c r="E26" s="56"/>
-      <c r="F26" s="56"/>
-      <c r="G26" s="57"/>
+      <c r="B26" s="57"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="20"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
@@ -2020,13 +2039,13 @@
       <c r="Z26" s="1"/>
     </row>
     <row r="27" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="19"/>
-      <c r="B27" s="20"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="56"/>
-      <c r="E27" s="56"/>
-      <c r="F27" s="56"/>
-      <c r="G27" s="57"/>
+      <c r="A27" s="38"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="20"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
@@ -2048,13 +2067,13 @@
       <c r="Z27" s="1"/>
     </row>
     <row r="28" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="28"/>
-      <c r="B28" s="29"/>
-      <c r="C28" s="59"/>
-      <c r="D28" s="60"/>
-      <c r="E28" s="60"/>
-      <c r="F28" s="60"/>
-      <c r="G28" s="61"/>
+      <c r="A28" s="48"/>
+      <c r="B28" s="49"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="23"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
@@ -2078,7 +2097,7 @@
     <row r="29" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
-      <c r="C29" s="58"/>
+      <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
@@ -8424,7 +8443,12 @@
     <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="19">
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A21:B22"/>
+    <mergeCell ref="C23:G23"/>
     <mergeCell ref="F21:G22"/>
     <mergeCell ref="C24:G28"/>
     <mergeCell ref="A3:B4"/>
@@ -8434,17 +8458,11 @@
     <mergeCell ref="C3:E4"/>
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F23:G23"/>
     <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C23:E23"/>
     <mergeCell ref="C21:E22"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A21:B22"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.22326454033771001" right="0.22326454033771001" top="0.20731707317073" bottom="0.22326454033771001" header="0" footer="0"/>
